--- a/example/data/data_season1.xlsx
+++ b/example/data/data_season1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ABM influenza\github\example data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pengl\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC09CC1-D0D4-4E2D-858B-F402989257D0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A655760A-AB7A-40F7-A2BF-84953C6AD2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>date</t>
   </si>
@@ -42,22 +42,19 @@
   <si>
     <t>new_absent</t>
   </si>
-  <si>
-    <t/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -65,7 +62,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -73,7 +70,7 @@
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri Light"/>
+      <name val="等线 Light"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="major"/>
@@ -82,7 +79,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -91,7 +88,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -100,7 +97,7 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -108,7 +105,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -116,7 +113,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -124,7 +121,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -132,7 +129,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -141,7 +138,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -150,7 +147,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -158,7 +155,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -167,7 +164,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -175,7 +172,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -184,7 +181,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -193,7 +190,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -201,14 +198,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -646,7 +643,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -654,48 +651,48 @@
     </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -711,7 +708,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1008,14 +1005,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H272"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="2" max="6" width="18.140625" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" customWidth="1"/>
+    <col min="2" max="6" width="18.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1038,7 +1035,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>39983</v>
       </c>
@@ -1057,12 +1054,10 @@
       <c r="F2" s="2">
         <v>1427.0763909969933</v>
       </c>
-      <c r="G2" s="3">
-        <v>82.346787213961804</v>
-      </c>
+      <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>39984</v>
       </c>
@@ -1081,12 +1076,10 @@
       <c r="F3" s="2">
         <v>1520.8156353252448</v>
       </c>
-      <c r="G3" s="3">
-        <v>4.1173393606980859</v>
-      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>39985</v>
       </c>
@@ -1105,12 +1098,10 @@
       <c r="F4" s="2">
         <v>1614.554555647298</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>39986</v>
       </c>
@@ -1129,12 +1120,10 @@
       <c r="F5" s="2">
         <v>1708.2944575934441</v>
       </c>
-      <c r="G5" s="3">
-        <v>178.08416674626764</v>
-      </c>
+      <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>39987</v>
       </c>
@@ -1153,12 +1142,10 @@
       <c r="F6" s="2">
         <v>1802.0333779154973</v>
       </c>
-      <c r="G6" s="3">
-        <v>195.89258342089474</v>
-      </c>
+      <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>39988</v>
       </c>
@@ -1177,12 +1164,10 @@
       <c r="F7" s="2">
         <v>1895.7732798616437</v>
       </c>
-      <c r="G7" s="3">
-        <v>142.46733339701427</v>
-      </c>
+      <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>39989</v>
       </c>
@@ -1201,12 +1186,10 @@
       <c r="F8" s="2">
         <v>1989.5122001836967</v>
       </c>
-      <c r="G8" s="3">
-        <v>189.95644452935267</v>
-      </c>
+      <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>39990</v>
       </c>
@@ -1225,12 +1208,10 @@
       <c r="F9" s="2">
         <v>2083.2514445119486</v>
       </c>
-      <c r="G9" s="3">
-        <v>47.489111132338124</v>
-      </c>
+      <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>39991</v>
       </c>
@@ -1249,12 +1230,10 @@
       <c r="F10" s="2">
         <v>2096.363709676592</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
+      <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>39992</v>
       </c>
@@ -1273,12 +1252,10 @@
       <c r="F11" s="2">
         <v>2109.4747418046495</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>39993</v>
       </c>
@@ -1297,12 +1274,10 @@
       <c r="F12" s="2">
         <v>2122.5870069692928</v>
       </c>
-      <c r="G12" s="3">
-        <v>126.8169012794139</v>
-      </c>
+      <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>39994</v>
       </c>
@@ -1321,12 +1296,10 @@
       <c r="F13" s="2">
         <v>2135.6977150911516</v>
       </c>
-      <c r="G13" s="3">
-        <v>109.90798110882577</v>
-      </c>
+      <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>39995</v>
       </c>
@@ -1345,12 +1318,10 @@
       <c r="F14" s="2">
         <v>2148.8099802557945</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>39996</v>
       </c>
@@ -1369,12 +1340,10 @@
       <c r="F15" s="2">
         <v>2161.9222358149404</v>
       </c>
-      <c r="G15" s="3">
-        <v>76.090140767648592</v>
-      </c>
+      <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>39997</v>
       </c>
@@ -1393,12 +1362,10 @@
       <c r="F16" s="2">
         <v>2175.0329439367993</v>
       </c>
-      <c r="G16" s="3">
-        <v>92.999060938236795</v>
-      </c>
+      <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>39998</v>
       </c>
@@ -1417,12 +1384,10 @@
       <c r="F17" s="2">
         <v>2274.6094527326595</v>
       </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>39999</v>
       </c>
@@ -1441,12 +1406,10 @@
       <c r="F18" s="2">
         <v>2374.1868155529719</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>40000</v>
       </c>
@@ -1465,12 +1428,10 @@
       <c r="F19" s="2">
         <v>2473.76307293634</v>
       </c>
-      <c r="G19" s="3">
-        <v>219.27302959356641</v>
-      </c>
+      <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>40001</v>
       </c>
@@ -1489,12 +1450,10 @@
       <c r="F20" s="2">
         <v>2573.3399057383986</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
+      <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>40002</v>
       </c>
@@ -1513,12 +1472,10 @@
       <c r="F21" s="2">
         <v>2672.916738540458</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
+      <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>40003</v>
       </c>
@@ -1537,12 +1494,10 @@
       <c r="F22" s="2">
         <v>2772.4935713425166</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
+      <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>40004</v>
       </c>
@@ -1561,12 +1516,10 @@
       <c r="F23" s="2">
         <v>2872.0709341628285</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
+      <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>40005</v>
       </c>
@@ -1585,12 +1538,10 @@
       <c r="F24" s="2">
         <v>2915.0547644993612</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
+      <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>40006</v>
       </c>
@@ -1609,12 +1560,10 @@
       <c r="F25" s="2">
         <v>2958.0397824720412</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>40007</v>
       </c>
@@ -1633,12 +1582,10 @@
       <c r="F26" s="2">
         <v>3001.0241428268268</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
+      <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>40008</v>
       </c>
@@ -1657,12 +1604,10 @@
       <c r="F27" s="2">
         <v>3044.0091607995073</v>
       </c>
-      <c r="G27" s="3">
-        <v>27.9767775872233</v>
-      </c>
+      <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>40009</v>
       </c>
@@ -1681,12 +1626,10 @@
       <c r="F28" s="2">
         <v>3086.9941787721873</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>40010</v>
       </c>
@@ -1705,12 +1648,10 @@
       <c r="F29" s="2">
         <v>3129.9782151207742</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>40011</v>
       </c>
@@ -1729,12 +1670,10 @@
       <c r="F30" s="2">
         <v>3172.9632330934546</v>
       </c>
-      <c r="G30" s="3">
-        <v>0</v>
-      </c>
+      <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>40012</v>
       </c>
@@ -1753,12 +1692,10 @@
       <c r="F31" s="2">
         <v>3299.2178732981024</v>
       </c>
-      <c r="G31" s="3">
-        <v>0</v>
-      </c>
+      <c r="G31" s="3"/>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>40013</v>
       </c>
@@ -1777,12 +1714,10 @@
       <c r="F32" s="2">
         <v>3425.4724777078104</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>40014</v>
       </c>
@@ -1801,12 +1736,10 @@
       <c r="F33" s="2">
         <v>3551.7268761054638</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
+      <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>40015</v>
       </c>
@@ -1825,12 +1758,10 @@
       <c r="F34" s="2">
         <v>3677.9806264907197</v>
       </c>
-      <c r="G34" s="3">
-        <v>0</v>
-      </c>
+      <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>40016</v>
       </c>
@@ -1849,12 +1780,10 @@
       <c r="F35" s="2">
         <v>3804.2357967136209</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
+      <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>40017</v>
       </c>
@@ -1873,12 +1802,10 @@
       <c r="F36" s="2">
         <v>3930.4898711050755</v>
       </c>
-      <c r="G36" s="3">
-        <v>0</v>
-      </c>
+      <c r="G36" s="3"/>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>40018</v>
       </c>
@@ -1897,12 +1824,10 @@
       <c r="F37" s="2">
         <v>4056.7447995209809</v>
       </c>
-      <c r="G37" s="3">
-        <v>0</v>
-      </c>
+      <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>40019</v>
       </c>
@@ -1921,12 +1846,10 @@
       <c r="F38" s="2">
         <v>4187.5070232281696</v>
       </c>
-      <c r="G38" s="3">
-        <v>0</v>
-      </c>
+      <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>40020</v>
       </c>
@@ -1945,12 +1868,10 @@
       <c r="F39" s="2">
         <v>4318.2678174922157</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G39" s="3"/>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>40021</v>
       </c>
@@ -1969,12 +1890,10 @@
       <c r="F40" s="2">
         <v>4449.0310228234966</v>
       </c>
-      <c r="G40" s="3">
-        <v>0</v>
-      </c>
+      <c r="G40" s="3"/>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40022</v>
       </c>
@@ -1993,12 +1912,10 @@
       <c r="F41" s="2">
         <v>4579.7923471057957</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
+      <c r="G41" s="3"/>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40023</v>
       </c>
@@ -2017,12 +1934,10 @@
       <c r="F42" s="2">
         <v>4710.554570812983</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
+      <c r="G42" s="3"/>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>40024</v>
       </c>
@@ -2041,12 +1956,10 @@
       <c r="F43" s="2">
         <v>4841.3168767193756</v>
       </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
+      <c r="G43" s="3"/>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>40025</v>
       </c>
@@ -2065,12 +1978,10 @@
       <c r="F44" s="2">
         <v>4972.0791004265629</v>
       </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
+      <c r="G44" s="3"/>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>40026</v>
       </c>
@@ -2089,12 +2000,10 @@
       <c r="F45" s="2">
         <v>5095.629211071735</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
+      <c r="G45" s="3"/>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>40027</v>
       </c>
@@ -2113,12 +2022,10 @@
       <c r="F46" s="2">
         <v>5219.1802211417971</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G46" s="3"/>
       <c r="H46" s="3"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>40028</v>
       </c>
@@ -2137,12 +2044,10 @@
       <c r="F47" s="2">
         <v>5342.730528193526</v>
       </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
+      <c r="G47" s="3"/>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>40029</v>
       </c>
@@ -2161,12 +2066,10 @@
       <c r="F48" s="2">
         <v>5466.2815382635881</v>
       </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
+      <c r="G48" s="3"/>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>40030</v>
       </c>
@@ -2185,12 +2088,10 @@
       <c r="F49" s="2">
         <v>5589.8319729149589</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
+      <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>40031</v>
       </c>
@@ -2209,12 +2110,10 @@
       <c r="F50" s="2">
         <v>5713.3835130032739</v>
       </c>
-      <c r="G50" s="3">
-        <v>0</v>
-      </c>
+      <c r="G50" s="3"/>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>40032</v>
       </c>
@@ -2233,12 +2132,10 @@
       <c r="F51" s="2">
         <v>5836.9339476546447</v>
       </c>
-      <c r="G51" s="3">
-        <v>0</v>
-      </c>
+      <c r="G51" s="3"/>
       <c r="H51" s="3"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>40033</v>
       </c>
@@ -2257,12 +2154,10 @@
       <c r="F52" s="2">
         <v>5686.2840354487535</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
+      <c r="G52" s="3"/>
       <c r="H52" s="3"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>40034</v>
       </c>
@@ -2281,12 +2176,10 @@
       <c r="F53" s="2">
         <v>5535.6328902062778</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G53" s="3"/>
       <c r="H53" s="3"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>40035</v>
       </c>
@@ -2305,12 +2198,10 @@
       <c r="F54" s="2">
         <v>5384.9827265878939</v>
       </c>
-      <c r="G54" s="3">
-        <v>0</v>
-      </c>
+      <c r="G54" s="3"/>
       <c r="H54" s="3"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>40036</v>
       </c>
@@ -2329,12 +2220,10 @@
       <c r="F55" s="2">
         <v>5234.3322389633122</v>
       </c>
-      <c r="G55" s="3">
-        <v>0</v>
-      </c>
+      <c r="G55" s="3"/>
       <c r="H55" s="3"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>40037</v>
       </c>
@@ -2353,12 +2242,10 @@
       <c r="F56" s="2">
         <v>5083.6810937208356</v>
       </c>
-      <c r="G56" s="3">
-        <v>0</v>
-      </c>
+      <c r="G56" s="3"/>
       <c r="H56" s="3"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>40038</v>
       </c>
@@ -2377,12 +2264,10 @@
       <c r="F57" s="2">
         <v>4933.0306060962539</v>
       </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
+      <c r="G57" s="3"/>
       <c r="H57" s="3"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>40039</v>
       </c>
@@ -2401,12 +2286,10 @@
       <c r="F58" s="2">
         <v>4782.3801184716713</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
+      <c r="G58" s="3"/>
       <c r="H58" s="3"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>40040</v>
       </c>
@@ -2425,12 +2308,10 @@
       <c r="F59" s="2">
         <v>5337.412272617139</v>
       </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
+      <c r="G59" s="3"/>
       <c r="H59" s="3"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>40041</v>
       </c>
@@ -2449,12 +2330,10 @@
       <c r="F60" s="2">
         <v>5892.4456597991921</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G60" s="3"/>
       <c r="H60" s="3"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>40042</v>
       </c>
@@ -2473,12 +2352,10 @@
       <c r="F61" s="2">
         <v>6447.4774899384593</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
+      <c r="G61" s="3"/>
       <c r="H61" s="3"/>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>40043</v>
       </c>
@@ -2497,12 +2374,10 @@
       <c r="F62" s="2">
         <v>7002.5108771205123</v>
       </c>
-      <c r="G62" s="3">
-        <v>142.93022208587959</v>
-      </c>
+      <c r="G62" s="3"/>
       <c r="H62" s="3"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>40044</v>
       </c>
@@ -2521,12 +2396,10 @@
       <c r="F63" s="2">
         <v>7557.5427072597813</v>
       </c>
-      <c r="G63" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G63" s="3"/>
       <c r="H63" s="3"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>40045</v>
       </c>
@@ -2545,12 +2418,10 @@
       <c r="F64" s="2">
         <v>8112.5755190231421</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G64" s="3"/>
       <c r="H64" s="3"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>40046</v>
       </c>
@@ -2569,12 +2440,10 @@
       <c r="F65" s="2">
         <v>8667.608906205196</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G65" s="3"/>
       <c r="H65" s="3"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>40047</v>
       </c>
@@ -2593,12 +2462,10 @@
       <c r="F66" s="2">
         <v>8810.0336186485492</v>
       </c>
-      <c r="G66" s="3">
-        <v>0</v>
-      </c>
+      <c r="G66" s="3"/>
       <c r="H66" s="3"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>40048</v>
       </c>
@@ -2617,12 +2484,10 @@
       <c r="F67" s="2">
         <v>8952.4586647036031</v>
       </c>
-      <c r="G67" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G67" s="3"/>
       <c r="H67" s="3"/>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>40049</v>
       </c>
@@ -2641,12 +2506,10 @@
       <c r="F68" s="2">
         <v>9094.8849341897403</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G68" s="3"/>
       <c r="H68" s="3"/>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>40050</v>
       </c>
@@ -2665,12 +2528,10 @@
       <c r="F69" s="2">
         <v>9237.3094502265412</v>
       </c>
-      <c r="G69" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G69" s="3"/>
       <c r="H69" s="3"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>40051</v>
       </c>
@@ -2689,12 +2550,10 @@
       <c r="F70" s="2">
         <v>9379.7348202877911</v>
       </c>
-      <c r="G70" s="3">
-        <v>0</v>
-      </c>
+      <c r="G70" s="3"/>
       <c r="H70" s="3"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>40052</v>
       </c>
@@ -2713,12 +2572,10 @@
       <c r="F71" s="2">
         <v>9522.1604321560353</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G71" s="3"/>
       <c r="H71" s="3"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>40053</v>
       </c>
@@ -2737,12 +2594,10 @@
       <c r="F72" s="2">
         <v>9664.5851542048877</v>
       </c>
-      <c r="G72" s="3">
-        <v>49.274074779614729</v>
-      </c>
+      <c r="G72" s="3"/>
       <c r="H72" s="3"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>40054</v>
       </c>
@@ -2761,12 +2616,10 @@
       <c r="F73" s="2">
         <v>9812.0536702348891</v>
       </c>
-      <c r="G73" s="3">
-        <v>0</v>
-      </c>
+      <c r="G73" s="3"/>
       <c r="H73" s="3"/>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>40055</v>
       </c>
@@ -2785,12 +2638,10 @@
       <c r="F74" s="2">
         <v>9959.5216562466358</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G74" s="3"/>
       <c r="H74" s="3"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>40056</v>
       </c>
@@ -2809,12 +2660,10 @@
       <c r="F75" s="2">
         <v>10106.989514658741</v>
       </c>
-      <c r="G75" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G75" s="3"/>
       <c r="H75" s="3"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>40057</v>
       </c>
@@ -2833,12 +2682,10 @@
       <c r="F76" s="2">
         <v>10254.45803068874</v>
       </c>
-      <c r="G76" s="3">
-        <v>533.69829538868669</v>
-      </c>
+      <c r="G76" s="3"/>
       <c r="H76" s="3"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>40058</v>
       </c>
@@ -2857,12 +2704,10 @@
       <c r="F77" s="2">
         <v>10401.92654671874</v>
       </c>
-      <c r="G77" s="3">
-        <v>477.51952745303561</v>
-      </c>
+      <c r="G77" s="3"/>
       <c r="H77" s="3"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>40059</v>
       </c>
@@ -2881,12 +2726,10 @@
       <c r="F78" s="2">
         <v>10549.393227100194</v>
       </c>
-      <c r="G78" s="3">
-        <v>561.78767935651217</v>
-      </c>
+      <c r="G78" s="3"/>
       <c r="H78" s="3"/>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>40060</v>
       </c>
@@ -2905,12 +2748,10 @@
       <c r="F79" s="2">
         <v>10696.861743130197</v>
       </c>
-      <c r="G79" s="3">
-        <v>589.87706332433766</v>
-      </c>
+      <c r="G79" s="3"/>
       <c r="H79" s="3"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>40061</v>
       </c>
@@ -2929,12 +2770,10 @@
       <c r="F80" s="2">
         <v>11533.253615761036</v>
       </c>
-      <c r="G80" s="3">
-        <v>0</v>
-      </c>
+      <c r="G80" s="3"/>
       <c r="H80" s="3"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>40062</v>
       </c>
@@ -2953,12 +2792,10 @@
       <c r="F81" s="2">
         <v>12369.64393134909</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G81" s="3"/>
       <c r="H81" s="3"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>40063</v>
       </c>
@@ -2977,12 +2814,10 @@
       <c r="F82" s="2">
         <v>13206.03580397993</v>
       </c>
-      <c r="G82" s="3">
-        <v>999.61698520268033</v>
-      </c>
+      <c r="G82" s="3"/>
       <c r="H82" s="3"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>40064</v>
       </c>
@@ -3001,12 +2836,10 @@
       <c r="F83" s="2">
         <v>14042.428206629023</v>
       </c>
-      <c r="G83" s="3">
-        <v>1230.2978279417648</v>
-      </c>
+      <c r="G83" s="3"/>
       <c r="H83" s="3"/>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>40065</v>
       </c>
@@ -3025,12 +2858,10 @@
       <c r="F84" s="2">
         <v>14878.819097635769</v>
       </c>
-      <c r="G84" s="3">
-        <v>1114.9574065722268</v>
-      </c>
+      <c r="G84" s="3"/>
       <c r="H84" s="3"/>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>40066</v>
       </c>
@@ -3049,12 +2880,10 @@
       <c r="F85" s="2">
         <v>15715.210070841718</v>
       </c>
-      <c r="G85" s="3">
-        <v>1191.8510208185855</v>
-      </c>
+      <c r="G85" s="3"/>
       <c r="H85" s="3"/>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>40067</v>
       </c>
@@ -3073,12 +2902,10 @@
       <c r="F86" s="2">
         <v>16551.601943472557</v>
       </c>
-      <c r="G86" s="3">
-        <v>1268.7446350649443</v>
-      </c>
+      <c r="G86" s="3"/>
       <c r="H86" s="3"/>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>40068</v>
       </c>
@@ -3097,12 +2924,10 @@
       <c r="F87" s="2">
         <v>17638.655216653562</v>
       </c>
-      <c r="G87" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G87" s="3"/>
       <c r="H87" s="3"/>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>40069</v>
       </c>
@@ -3121,12 +2946,10 @@
       <c r="F88" s="2">
         <v>18725.708165828368</v>
       </c>
-      <c r="G88" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G88" s="3"/>
       <c r="H88" s="3"/>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>40070</v>
       </c>
@@ -3145,12 +2968,10 @@
       <c r="F89" s="2">
         <v>19812.760539584484</v>
       </c>
-      <c r="G89" s="3">
-        <v>2509.068084830049</v>
-      </c>
+      <c r="G89" s="3"/>
       <c r="H89" s="3"/>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>40071</v>
       </c>
@@ -3169,12 +2990,10 @@
       <c r="F90" s="2">
         <v>20899.814342783742</v>
       </c>
-      <c r="G90" s="3">
-        <v>373.6909913576672</v>
-      </c>
+      <c r="G90" s="3"/>
       <c r="H90" s="3"/>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>40072</v>
       </c>
@@ -3193,12 +3012,10 @@
       <c r="F91" s="2">
         <v>21986.866716539855</v>
       </c>
-      <c r="G91" s="3">
-        <v>2081.9926661355739</v>
-      </c>
+      <c r="G91" s="3"/>
       <c r="H91" s="3"/>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>40073</v>
       </c>
@@ -3217,12 +3034,10 @@
       <c r="F92" s="2">
         <v>23073.919665714664</v>
       </c>
-      <c r="G92" s="3">
-        <v>2242.1459481459997</v>
-      </c>
+      <c r="G92" s="3"/>
       <c r="H92" s="3"/>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>40074</v>
       </c>
@@ -3241,12 +3056,10 @@
       <c r="F93" s="2">
         <v>24160.972938895666</v>
       </c>
-      <c r="G93" s="3">
-        <v>2242.1459481459997</v>
-      </c>
+      <c r="G93" s="3"/>
       <c r="H93" s="3"/>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>40075</v>
       </c>
@@ -3265,12 +3078,10 @@
       <c r="F94" s="2">
         <v>24579.34064631151</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
+      <c r="G94" s="3"/>
       <c r="H94" s="3"/>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>40076</v>
       </c>
@@ -3289,12 +3100,10 @@
       <c r="F95" s="2">
         <v>24997.705942660119</v>
       </c>
-      <c r="G95" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G95" s="3"/>
       <c r="H95" s="3"/>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>40077</v>
       </c>
@@ -3313,12 +3122,10 @@
       <c r="F96" s="2">
         <v>25416.073650075959</v>
       </c>
-      <c r="G96" s="3">
-        <v>3887.826551142025</v>
-      </c>
+      <c r="G96" s="3"/>
       <c r="H96" s="3"/>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>40078</v>
       </c>
@@ -3337,12 +3144,10 @@
       <c r="F97" s="2">
         <v>25834.440375867714</v>
       </c>
-      <c r="G97" s="3">
-        <v>4009.3211308652103</v>
-      </c>
+      <c r="G97" s="3"/>
       <c r="H97" s="3"/>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>40079</v>
       </c>
@@ -3361,12 +3166,10 @@
       <c r="F98" s="2">
         <v>26252.807229259106</v>
       </c>
-      <c r="G98" s="3">
-        <v>3584.0901018340569</v>
-      </c>
+      <c r="G98" s="3"/>
       <c r="H98" s="3"/>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>40080</v>
       </c>
@@ -3385,12 +3188,10 @@
       <c r="F99" s="2">
         <v>26671.174279057053</v>
       </c>
-      <c r="G99" s="3">
-        <v>3523.3428119724599</v>
-      </c>
+      <c r="G99" s="3"/>
       <c r="H99" s="3"/>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>40081</v>
       </c>
@@ -3409,12 +3210,10 @@
       <c r="F100" s="2">
         <v>27089.541456454641</v>
       </c>
-      <c r="G100" s="3">
-        <v>3098.111782941297</v>
-      </c>
+      <c r="G100" s="3"/>
       <c r="H100" s="3"/>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>40082</v>
       </c>
@@ -3433,12 +3232,10 @@
       <c r="F101" s="2">
         <v>26418.88695681834</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
+      <c r="G101" s="3"/>
       <c r="H101" s="3"/>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>40083</v>
       </c>
@@ -3457,12 +3254,10 @@
       <c r="F102" s="2">
         <v>25748.232584781668</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G102" s="3"/>
       <c r="H102" s="3"/>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>40084</v>
       </c>
@@ -3481,12 +3276,10 @@
       <c r="F103" s="2">
         <v>25077.577231120918</v>
       </c>
-      <c r="G103" s="3">
-        <v>2411.0358151699998</v>
-      </c>
+      <c r="G103" s="3"/>
       <c r="H103" s="3"/>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>40085</v>
       </c>
@@ -3505,12 +3298,10 @@
       <c r="F104" s="2">
         <v>24406.923389102507</v>
       </c>
-      <c r="G104" s="3">
-        <v>2361.8310026155114</v>
-      </c>
+      <c r="G104" s="3"/>
       <c r="H104" s="3"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>40086</v>
       </c>
@@ -3529,12 +3320,10 @@
       <c r="F105" s="2">
         <v>23736.268359447946</v>
       </c>
-      <c r="G105" s="3">
-        <v>1820.578064516124</v>
-      </c>
+      <c r="G105" s="3"/>
       <c r="H105" s="3"/>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>40087</v>
       </c>
@@ -3553,12 +3342,10 @@
       <c r="F106" s="2">
         <v>23065.613663405089</v>
       </c>
-      <c r="G106" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G106" s="3"/>
       <c r="H106" s="3"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>40088</v>
       </c>
@@ -3577,12 +3364,10 @@
       <c r="F107" s="2">
         <v>22394.959163768781</v>
       </c>
-      <c r="G107" s="3">
-        <v>2706.2646904969374</v>
-      </c>
+      <c r="G107" s="3"/>
       <c r="H107" s="3"/>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>40089</v>
       </c>
@@ -3601,12 +3386,10 @@
       <c r="F108" s="2">
         <v>20803.307189619354</v>
       </c>
-      <c r="G108" s="3">
-        <v>0</v>
-      </c>
+      <c r="G108" s="3"/>
       <c r="H108" s="3"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>40090</v>
       </c>
@@ -3625,12 +3408,10 @@
       <c r="F109" s="2">
         <v>19211.655411876483</v>
       </c>
-      <c r="G109" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G109" s="3"/>
       <c r="H109" s="3"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>40091</v>
       </c>
@@ -3649,12 +3430,10 @@
       <c r="F110" s="2">
         <v>17620.003761733253</v>
       </c>
-      <c r="G110" s="3">
-        <v>1054.9397886560582</v>
-      </c>
+      <c r="G110" s="3"/>
       <c r="H110" s="3"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>40092</v>
       </c>
@@ -3673,12 +3452,10 @@
       <c r="F111" s="2">
         <v>16028.351659984182</v>
       </c>
-      <c r="G111" s="3">
-        <v>1029.8221746404402</v>
-      </c>
+      <c r="G111" s="3"/>
       <c r="H111" s="3"/>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>40093</v>
       </c>
@@ -3697,12 +3474,10 @@
       <c r="F112" s="2">
         <v>14436.700009840953</v>
       </c>
-      <c r="G112" s="3">
-        <v>778.646034484236</v>
-      </c>
+      <c r="G112" s="3"/>
       <c r="H112" s="3"/>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>40094</v>
       </c>
@@ -3721,12 +3496,10 @@
       <c r="F113" s="2">
         <v>12845.048565709778</v>
       </c>
-      <c r="G113" s="3">
-        <v>778.646034484236</v>
-      </c>
+      <c r="G113" s="3"/>
       <c r="H113" s="3"/>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>40095</v>
       </c>
@@ -3745,12 +3518,10 @@
       <c r="F114" s="2">
         <v>11253.396833367347</v>
       </c>
-      <c r="G114" s="3">
-        <v>728.41080645299451</v>
-      </c>
+      <c r="G114" s="3"/>
       <c r="H114" s="3"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>40096</v>
       </c>
@@ -3769,12 +3540,10 @@
       <c r="F115" s="2">
         <v>10507.694671527774</v>
       </c>
-      <c r="G115" s="3">
-        <v>0</v>
-      </c>
+      <c r="G115" s="3"/>
       <c r="H115" s="3"/>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>40097</v>
       </c>
@@ -3793,12 +3562,10 @@
       <c r="F116" s="2">
         <v>9761.9925096882016</v>
       </c>
-      <c r="G116" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G116" s="3"/>
       <c r="H116" s="3"/>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>40098</v>
       </c>
@@ -3817,12 +3584,10 @@
       <c r="F117" s="2">
         <v>9016.290923267321</v>
       </c>
-      <c r="G117" s="3">
-        <v>410.78069361182844</v>
-      </c>
+      <c r="G117" s="3"/>
       <c r="H117" s="3"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>40099</v>
       </c>
@@ -3841,12 +3606,10 @@
       <c r="F118" s="2">
         <v>8270.5884278160538</v>
       </c>
-      <c r="G118" s="3">
-        <v>331.27475291276477</v>
-      </c>
+      <c r="G118" s="3"/>
       <c r="H118" s="3"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>40100</v>
       </c>
@@ -3865,12 +3628,10 @@
       <c r="F119" s="2">
         <v>7524.8871654013701</v>
       </c>
-      <c r="G119" s="3">
-        <v>304.77277267974347</v>
-      </c>
+      <c r="G119" s="3"/>
       <c r="H119" s="3"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>40101</v>
       </c>
@@ -3889,12 +3650,10 @@
       <c r="F120" s="2">
         <v>6779.1846795555994</v>
       </c>
-      <c r="G120" s="3">
-        <v>318.02376279625412</v>
-      </c>
+      <c r="G120" s="3"/>
       <c r="H120" s="3"/>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>40102</v>
       </c>
@@ -3913,12 +3672,10 @@
       <c r="F121" s="2">
         <v>6033.482841722227</v>
       </c>
-      <c r="G121" s="3">
-        <v>344.52574302927536</v>
-      </c>
+      <c r="G121" s="3"/>
       <c r="H121" s="3"/>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>40103</v>
       </c>
@@ -3937,12 +3694,10 @@
       <c r="F122" s="2">
         <v>5700.4265707454988</v>
       </c>
-      <c r="G122" s="3">
-        <v>0</v>
-      </c>
+      <c r="G122" s="3"/>
       <c r="H122" s="3"/>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>40104</v>
       </c>
@@ -3961,12 +3716,10 @@
       <c r="F123" s="2">
         <v>5367.3687427259856</v>
       </c>
-      <c r="G123" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G123" s="3"/>
       <c r="H123" s="3"/>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>40105</v>
       </c>
@@ -3985,12 +3738,10 @@
       <c r="F124" s="2">
         <v>5034.311896330566</v>
       </c>
-      <c r="G124" s="3">
-        <v>192.36705667693059</v>
-      </c>
+      <c r="G124" s="3"/>
       <c r="H124" s="3"/>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>40106</v>
       </c>
@@ -4009,12 +3760,10 @@
       <c r="F125" s="2">
         <v>4701.2550499351455</v>
       </c>
-      <c r="G125" s="3">
-        <v>176.97769214277645</v>
-      </c>
+      <c r="G125" s="3"/>
       <c r="H125" s="3"/>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>40107</v>
       </c>
@@ -4033,12 +3782,10 @@
       <c r="F126" s="2">
         <v>4368.1978795335262</v>
       </c>
-      <c r="G126" s="3">
-        <v>161.58832760862146</v>
-      </c>
+      <c r="G126" s="3"/>
       <c r="H126" s="3"/>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>40108</v>
       </c>
@@ -4057,12 +3804,10 @@
       <c r="F127" s="2">
         <v>4035.1407091319079</v>
       </c>
-      <c r="G127" s="3">
-        <v>146.19896307446731</v>
-      </c>
+      <c r="G127" s="3"/>
       <c r="H127" s="3"/>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>40109</v>
       </c>
@@ -4081,12 +3826,10 @@
       <c r="F128" s="2">
         <v>3702.0847621613775</v>
       </c>
-      <c r="G128" s="3">
-        <v>176.97769214277645</v>
-      </c>
+      <c r="G128" s="3"/>
       <c r="H128" s="3"/>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>40110</v>
       </c>
@@ -4105,12 +3848,10 @@
       <c r="F129" s="2">
         <v>3569.4718256679143</v>
       </c>
-      <c r="G129" s="3">
-        <v>0</v>
-      </c>
+      <c r="G129" s="3"/>
       <c r="H129" s="3"/>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>40111</v>
       </c>
@@ -4129,12 +3870,10 @@
       <c r="F130" s="2">
         <v>3436.8588891744512</v>
       </c>
-      <c r="G130" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G130" s="3"/>
       <c r="H130" s="3"/>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>40112</v>
       </c>
@@ -4153,12 +3892,10 @@
       <c r="F131" s="2">
         <v>3304.2461944879838</v>
       </c>
-      <c r="G131" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G131" s="3"/>
       <c r="H131" s="3"/>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>40113</v>
       </c>
@@ -4177,12 +3914,10 @@
       <c r="F132" s="2">
         <v>3171.633788012773</v>
       </c>
-      <c r="G132" s="3">
-        <v>113.48997311559911</v>
-      </c>
+      <c r="G132" s="3"/>
       <c r="H132" s="3"/>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>40114</v>
       </c>
@@ -4201,12 +3936,10 @@
       <c r="F133" s="2">
         <v>3039.0217509442</v>
       </c>
-      <c r="G133" s="3">
-        <v>118.89425754967561</v>
-      </c>
+      <c r="G133" s="3"/>
       <c r="H133" s="3"/>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>40115</v>
       </c>
@@ -4225,12 +3958,10 @@
       <c r="F134" s="2">
         <v>2906.4088144507373</v>
       </c>
-      <c r="G134" s="3">
-        <v>108.08568868152344</v>
-      </c>
+      <c r="G134" s="3"/>
       <c r="H134" s="3"/>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>40116</v>
       </c>
@@ -4249,12 +3980,10 @@
       <c r="F135" s="2">
         <v>2773.7971013883625</v>
       </c>
-      <c r="G135" s="3">
-        <v>102.68140424744693</v>
-      </c>
+      <c r="G135" s="3"/>
       <c r="H135" s="3"/>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>40117</v>
       </c>
@@ -4273,12 +4002,10 @@
       <c r="F136" s="2">
         <v>2583.2961945169873</v>
       </c>
-      <c r="G136" s="3">
-        <v>0</v>
-      </c>
+      <c r="G136" s="3"/>
       <c r="H136" s="3"/>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>40118</v>
       </c>
@@ -4297,12 +4024,10 @@
       <c r="F137" s="2">
         <v>2392.797492700794</v>
       </c>
-      <c r="G137" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G137" s="3"/>
       <c r="H137" s="3"/>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>40119</v>
       </c>
@@ -4321,12 +4046,10 @@
       <c r="F138" s="2">
         <v>2202.296909835618</v>
       </c>
-      <c r="G138" s="3">
-        <v>53.475237903863572</v>
-      </c>
+      <c r="G138" s="3"/>
       <c r="H138" s="3"/>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>40120</v>
       </c>
@@ -4345,12 +4068,10 @@
       <c r="F139" s="2">
         <v>2011.7975504015294</v>
       </c>
-      <c r="G139" s="3">
-        <v>59.10421031479661</v>
-      </c>
+      <c r="G139" s="3"/>
       <c r="H139" s="3"/>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>40121</v>
       </c>
@@ -4369,12 +4090,10 @@
       <c r="F140" s="2">
         <v>1821.2988485853357</v>
       </c>
-      <c r="G140" s="3">
-        <v>70.362155136662579</v>
-      </c>
+      <c r="G140" s="3"/>
       <c r="H140" s="3"/>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>40122</v>
       </c>
@@ -4393,12 +4112,10 @@
       <c r="F141" s="2">
         <v>1630.7982657201596</v>
       </c>
-      <c r="G141" s="3">
-        <v>56.289724109330088</v>
-      </c>
+      <c r="G141" s="3"/>
       <c r="H141" s="3"/>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>40123</v>
       </c>
@@ -4417,12 +4134,10 @@
       <c r="F142" s="2">
         <v>1440.2989062860713</v>
       </c>
-      <c r="G142" s="3">
-        <v>61.918696520263126</v>
-      </c>
+      <c r="G142" s="3"/>
       <c r="H142" s="3"/>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>40124</v>
       </c>
@@ -4441,12 +4156,10 @@
       <c r="F143" s="2">
         <v>1381.2470497151703</v>
       </c>
-      <c r="G143" s="3">
-        <v>160.42571371159124</v>
-      </c>
+      <c r="G143" s="3"/>
       <c r="H143" s="3"/>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>40125</v>
       </c>
@@ -4465,12 +4178,10 @@
       <c r="F144" s="2">
         <v>1322.1958865571046</v>
       </c>
-      <c r="G144" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G144" s="3"/>
       <c r="H144" s="3"/>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>40126</v>
       </c>
@@ -4489,12 +4200,10 @@
       <c r="F145" s="2">
         <v>1263.1449294110935</v>
       </c>
-      <c r="G145" s="3">
-        <v>42.646119987580988</v>
-      </c>
+      <c r="G145" s="3"/>
       <c r="H145" s="3"/>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>40127</v>
       </c>
@@ -4513,12 +4222,10 @@
       <c r="F146" s="2">
         <v>1204.0928668281381</v>
       </c>
-      <c r="G146" s="3">
-        <v>38.584584750668562</v>
-      </c>
+      <c r="G146" s="3"/>
       <c r="H146" s="3"/>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>40128</v>
       </c>
@@ -4537,12 +4244,10 @@
       <c r="F147" s="2">
         <v>1145.0417036700726</v>
       </c>
-      <c r="G147" s="3">
-        <v>34.52304951375605</v>
-      </c>
+      <c r="G147" s="3"/>
       <c r="H147" s="3"/>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>40129</v>
       </c>
@@ -4561,12 +4266,10 @@
       <c r="F148" s="2">
         <v>1085.9910705302598</v>
       </c>
-      <c r="G148" s="3">
-        <v>36.553817132212266</v>
-      </c>
+      <c r="G148" s="3"/>
       <c r="H148" s="3"/>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>40130</v>
       </c>
@@ -4585,12 +4288,10 @@
       <c r="F149" s="2">
         <v>1026.9219188744012</v>
       </c>
-      <c r="G149" s="3">
-        <v>38.584584750668562</v>
-      </c>
+      <c r="G149" s="3"/>
       <c r="H149" s="3"/>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>40131</v>
       </c>
@@ -4609,12 +4310,10 @@
       <c r="F150" s="2">
         <v>1101.416784059546</v>
       </c>
-      <c r="G150" s="3">
-        <v>0</v>
-      </c>
+      <c r="G150" s="3"/>
       <c r="H150" s="3"/>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>40132</v>
       </c>
@@ -4633,12 +4332,10 @@
       <c r="F151" s="2">
         <v>1175.8941123527381</v>
       </c>
-      <c r="G151" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="G151" s="3"/>
       <c r="H151" s="3"/>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>40133</v>
       </c>
@@ -4657,12 +4354,10 @@
       <c r="F152" s="2">
         <v>1250.3722220766756</v>
       </c>
-      <c r="G152" s="3">
-        <v>84.558114906219274</v>
-      </c>
+      <c r="G152" s="3"/>
       <c r="H152" s="3"/>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>40134</v>
       </c>
@@ -4681,12 +4376,10 @@
       <c r="F153" s="2">
         <v>1324.8495503698678</v>
       </c>
-      <c r="G153" s="3">
-        <v>72.03098677196455</v>
-      </c>
+      <c r="G153" s="3"/>
       <c r="H153" s="3"/>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>40135</v>
       </c>
@@ -4705,12 +4398,10 @@
       <c r="F154" s="2">
         <v>1399.3273264821091</v>
       </c>
-      <c r="G154" s="3">
-        <v>78.294550839091926</v>
-      </c>
+      <c r="G154" s="3"/>
       <c r="H154" s="3"/>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>40136</v>
       </c>
@@ -4729,12 +4420,10 @@
       <c r="F155" s="2">
         <v>1473.8046547753015</v>
       </c>
-      <c r="G155" s="3">
-        <v>84.558114906219274</v>
-      </c>
+      <c r="G155" s="3"/>
       <c r="H155" s="3"/>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>40137</v>
       </c>
@@ -4753,12 +4442,10 @@
       <c r="F156" s="2">
         <v>1548.282764499239</v>
       </c>
-      <c r="G156" s="3">
-        <v>112.74415320829249</v>
-      </c>
+      <c r="G156" s="3"/>
       <c r="H156" s="3"/>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>40138</v>
       </c>
@@ -4777,12 +4464,10 @@
       <c r="F157" s="2">
         <v>5216.4981660387893</v>
       </c>
-      <c r="G157" s="3">
-        <v>0</v>
-      </c>
+      <c r="G157" s="3"/>
       <c r="H157" s="3"/>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -4792,7 +4477,7 @@
       <c r="G158" s="3"/>
       <c r="H158" s="3"/>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -4802,7 +4487,7 @@
       <c r="G159" s="3"/>
       <c r="H159" s="3"/>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -4812,7 +4497,7 @@
       <c r="G160" s="3"/>
       <c r="H160" s="3"/>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -4822,7 +4507,7 @@
       <c r="G161" s="3"/>
       <c r="H161" s="3"/>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -4832,7 +4517,7 @@
       <c r="G162" s="3"/>
       <c r="H162" s="3"/>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -4842,7 +4527,7 @@
       <c r="G163" s="3"/>
       <c r="H163" s="3"/>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -4852,7 +4537,7 @@
       <c r="G164" s="3"/>
       <c r="H164" s="3"/>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -4862,7 +4547,7 @@
       <c r="G165" s="3"/>
       <c r="H165" s="3"/>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -4872,7 +4557,7 @@
       <c r="G166" s="3"/>
       <c r="H166" s="3"/>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -4882,7 +4567,7 @@
       <c r="G167" s="3"/>
       <c r="H167" s="3"/>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -4892,7 +4577,7 @@
       <c r="G168" s="3"/>
       <c r="H168" s="3"/>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -4902,7 +4587,7 @@
       <c r="G169" s="3"/>
       <c r="H169" s="3"/>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -4912,7 +4597,7 @@
       <c r="G170" s="3"/>
       <c r="H170" s="3"/>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -4922,7 +4607,7 @@
       <c r="G171" s="3"/>
       <c r="H171" s="3"/>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -4932,7 +4617,7 @@
       <c r="G172" s="3"/>
       <c r="H172" s="3"/>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -4942,7 +4627,7 @@
       <c r="G173" s="3"/>
       <c r="H173" s="3"/>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -4952,7 +4637,7 @@
       <c r="G174" s="3"/>
       <c r="H174" s="3"/>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -4962,7 +4647,7 @@
       <c r="G175" s="3"/>
       <c r="H175" s="3"/>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -4972,7 +4657,7 @@
       <c r="G176" s="3"/>
       <c r="H176" s="3"/>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -4982,7 +4667,7 @@
       <c r="G177" s="3"/>
       <c r="H177" s="3"/>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -4992,7 +4677,7 @@
       <c r="G178" s="3"/>
       <c r="H178" s="3"/>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -5002,7 +4687,7 @@
       <c r="G179" s="3"/>
       <c r="H179" s="3"/>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -5012,7 +4697,7 @@
       <c r="G180" s="3"/>
       <c r="H180" s="3"/>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -5022,7 +4707,7 @@
       <c r="G181" s="3"/>
       <c r="H181" s="3"/>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -5032,7 +4717,7 @@
       <c r="G182" s="3"/>
       <c r="H182" s="3"/>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -5042,7 +4727,7 @@
       <c r="G183" s="3"/>
       <c r="H183" s="3"/>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -5052,7 +4737,7 @@
       <c r="G184" s="3"/>
       <c r="H184" s="3"/>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -5062,7 +4747,7 @@
       <c r="G185" s="3"/>
       <c r="H185" s="3"/>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -5072,7 +4757,7 @@
       <c r="G186" s="3"/>
       <c r="H186" s="3"/>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -5082,7 +4767,7 @@
       <c r="G187" s="3"/>
       <c r="H187" s="3"/>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -5092,7 +4777,7 @@
       <c r="G188" s="3"/>
       <c r="H188" s="3"/>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -5102,7 +4787,7 @@
       <c r="G189" s="3"/>
       <c r="H189" s="3"/>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -5112,7 +4797,7 @@
       <c r="G190" s="3"/>
       <c r="H190" s="3"/>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -5122,7 +4807,7 @@
       <c r="G191" s="3"/>
       <c r="H191" s="3"/>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -5132,7 +4817,7 @@
       <c r="G192" s="3"/>
       <c r="H192" s="3"/>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -5142,7 +4827,7 @@
       <c r="G193" s="3"/>
       <c r="H193" s="3"/>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -5152,7 +4837,7 @@
       <c r="G194" s="3"/>
       <c r="H194" s="3"/>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -5162,7 +4847,7 @@
       <c r="G195" s="3"/>
       <c r="H195" s="3"/>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -5172,7 +4857,7 @@
       <c r="G196" s="3"/>
       <c r="H196" s="3"/>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -5182,7 +4867,7 @@
       <c r="G197" s="3"/>
       <c r="H197" s="3"/>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -5192,7 +4877,7 @@
       <c r="G198" s="3"/>
       <c r="H198" s="3"/>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -5202,7 +4887,7 @@
       <c r="G199" s="3"/>
       <c r="H199" s="3"/>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -5212,7 +4897,7 @@
       <c r="G200" s="3"/>
       <c r="H200" s="3"/>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -5222,7 +4907,7 @@
       <c r="G201" s="3"/>
       <c r="H201" s="3"/>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -5232,7 +4917,7 @@
       <c r="G202" s="3"/>
       <c r="H202" s="3"/>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -5242,7 +4927,7 @@
       <c r="G203" s="3"/>
       <c r="H203" s="3"/>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -5252,7 +4937,7 @@
       <c r="G204" s="3"/>
       <c r="H204" s="3"/>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -5262,7 +4947,7 @@
       <c r="G205" s="3"/>
       <c r="H205" s="3"/>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -5272,7 +4957,7 @@
       <c r="G206" s="3"/>
       <c r="H206" s="3"/>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -5282,7 +4967,7 @@
       <c r="G207" s="3"/>
       <c r="H207" s="3"/>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -5292,7 +4977,7 @@
       <c r="G208" s="3"/>
       <c r="H208" s="3"/>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -5302,7 +4987,7 @@
       <c r="G209" s="3"/>
       <c r="H209" s="3"/>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -5312,7 +4997,7 @@
       <c r="G210" s="3"/>
       <c r="H210" s="3"/>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -5322,7 +5007,7 @@
       <c r="G211" s="3"/>
       <c r="H211" s="3"/>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -5332,7 +5017,7 @@
       <c r="G212" s="3"/>
       <c r="H212" s="3"/>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -5342,7 +5027,7 @@
       <c r="G213" s="3"/>
       <c r="H213" s="3"/>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -5352,7 +5037,7 @@
       <c r="G214" s="3"/>
       <c r="H214" s="3"/>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -5362,7 +5047,7 @@
       <c r="G215" s="3"/>
       <c r="H215" s="3"/>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -5372,7 +5057,7 @@
       <c r="G216" s="3"/>
       <c r="H216" s="3"/>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -5382,7 +5067,7 @@
       <c r="G217" s="3"/>
       <c r="H217" s="3"/>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -5392,7 +5077,7 @@
       <c r="G218" s="3"/>
       <c r="H218" s="3"/>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -5402,7 +5087,7 @@
       <c r="G219" s="3"/>
       <c r="H219" s="3"/>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -5412,7 +5097,7 @@
       <c r="G220" s="3"/>
       <c r="H220" s="3"/>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -5422,7 +5107,7 @@
       <c r="G221" s="3"/>
       <c r="H221" s="3"/>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -5432,7 +5117,7 @@
       <c r="G222" s="3"/>
       <c r="H222" s="3"/>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -5442,7 +5127,7 @@
       <c r="G223" s="3"/>
       <c r="H223" s="3"/>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -5452,7 +5137,7 @@
       <c r="G224" s="3"/>
       <c r="H224" s="3"/>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -5462,7 +5147,7 @@
       <c r="G225" s="3"/>
       <c r="H225" s="3"/>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -5472,7 +5157,7 @@
       <c r="G226" s="3"/>
       <c r="H226" s="3"/>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -5482,7 +5167,7 @@
       <c r="G227" s="3"/>
       <c r="H227" s="3"/>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -5492,7 +5177,7 @@
       <c r="G228" s="3"/>
       <c r="H228" s="3"/>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -5502,7 +5187,7 @@
       <c r="G229" s="3"/>
       <c r="H229" s="3"/>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -5512,7 +5197,7 @@
       <c r="G230" s="3"/>
       <c r="H230" s="3"/>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -5522,7 +5207,7 @@
       <c r="G231" s="3"/>
       <c r="H231" s="3"/>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -5532,7 +5217,7 @@
       <c r="G232" s="3"/>
       <c r="H232" s="3"/>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -5542,7 +5227,7 @@
       <c r="G233" s="3"/>
       <c r="H233" s="3"/>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -5552,7 +5237,7 @@
       <c r="G234" s="3"/>
       <c r="H234" s="3"/>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -5562,7 +5247,7 @@
       <c r="G235" s="3"/>
       <c r="H235" s="3"/>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -5572,7 +5257,7 @@
       <c r="G236" s="3"/>
       <c r="H236" s="3"/>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -5582,7 +5267,7 @@
       <c r="G237" s="3"/>
       <c r="H237" s="3"/>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -5592,7 +5277,7 @@
       <c r="G238" s="3"/>
       <c r="H238" s="3"/>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -5602,7 +5287,7 @@
       <c r="G239" s="3"/>
       <c r="H239" s="3"/>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -5612,7 +5297,7 @@
       <c r="G240" s="3"/>
       <c r="H240" s="3"/>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -5622,7 +5307,7 @@
       <c r="G241" s="3"/>
       <c r="H241" s="3"/>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -5632,7 +5317,7 @@
       <c r="G242" s="3"/>
       <c r="H242" s="3"/>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -5642,7 +5327,7 @@
       <c r="G243" s="3"/>
       <c r="H243" s="3"/>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -5652,7 +5337,7 @@
       <c r="G244" s="3"/>
       <c r="H244" s="3"/>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -5662,7 +5347,7 @@
       <c r="G245" s="3"/>
       <c r="H245" s="3"/>
     </row>
-    <row r="246" spans="1:8">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -5672,7 +5357,7 @@
       <c r="G246" s="3"/>
       <c r="H246" s="3"/>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -5682,7 +5367,7 @@
       <c r="G247" s="3"/>
       <c r="H247" s="3"/>
     </row>
-    <row r="248" spans="1:8">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -5692,7 +5377,7 @@
       <c r="G248" s="3"/>
       <c r="H248" s="3"/>
     </row>
-    <row r="249" spans="1:8">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -5702,7 +5387,7 @@
       <c r="G249" s="3"/>
       <c r="H249" s="3"/>
     </row>
-    <row r="250" spans="1:8">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -5712,7 +5397,7 @@
       <c r="G250" s="3"/>
       <c r="H250" s="3"/>
     </row>
-    <row r="251" spans="1:8">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -5722,7 +5407,7 @@
       <c r="G251" s="3"/>
       <c r="H251" s="3"/>
     </row>
-    <row r="252" spans="1:8">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -5732,7 +5417,7 @@
       <c r="G252" s="3"/>
       <c r="H252" s="3"/>
     </row>
-    <row r="253" spans="1:8">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -5742,7 +5427,7 @@
       <c r="G253" s="3"/>
       <c r="H253" s="3"/>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -5752,7 +5437,7 @@
       <c r="G254" s="3"/>
       <c r="H254" s="3"/>
     </row>
-    <row r="255" spans="1:8">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -5762,7 +5447,7 @@
       <c r="G255" s="3"/>
       <c r="H255" s="3"/>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -5772,7 +5457,7 @@
       <c r="G256" s="3"/>
       <c r="H256" s="3"/>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -5782,7 +5467,7 @@
       <c r="G257" s="3"/>
       <c r="H257" s="3"/>
     </row>
-    <row r="258" spans="1:8">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -5792,7 +5477,7 @@
       <c r="G258" s="3"/>
       <c r="H258" s="3"/>
     </row>
-    <row r="259" spans="1:8">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -5802,7 +5487,7 @@
       <c r="G259" s="3"/>
       <c r="H259" s="3"/>
     </row>
-    <row r="260" spans="1:8">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -5812,7 +5497,7 @@
       <c r="G260" s="3"/>
       <c r="H260" s="3"/>
     </row>
-    <row r="261" spans="1:8">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -5822,7 +5507,7 @@
       <c r="G261" s="3"/>
       <c r="H261" s="3"/>
     </row>
-    <row r="262" spans="1:8">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -5832,7 +5517,7 @@
       <c r="G262" s="3"/>
       <c r="H262" s="3"/>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -5842,7 +5527,7 @@
       <c r="G263" s="3"/>
       <c r="H263" s="3"/>
     </row>
-    <row r="264" spans="1:8">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -5852,7 +5537,7 @@
       <c r="G264" s="3"/>
       <c r="H264" s="3"/>
     </row>
-    <row r="265" spans="1:8">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -5862,7 +5547,7 @@
       <c r="G265" s="3"/>
       <c r="H265" s="3"/>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -5872,7 +5557,7 @@
       <c r="G266" s="3"/>
       <c r="H266" s="3"/>
     </row>
-    <row r="267" spans="1:8">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -5882,7 +5567,7 @@
       <c r="G267" s="3"/>
       <c r="H267" s="3"/>
     </row>
-    <row r="268" spans="1:8">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -5892,7 +5577,7 @@
       <c r="G268" s="3"/>
       <c r="H268" s="3"/>
     </row>
-    <row r="269" spans="1:8">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -5902,7 +5587,7 @@
       <c r="G269" s="3"/>
       <c r="H269" s="3"/>
     </row>
-    <row r="270" spans="1:8">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -5912,7 +5597,7 @@
       <c r="G270" s="3"/>
       <c r="H270" s="3"/>
     </row>
-    <row r="271" spans="1:8">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -5922,7 +5607,7 @@
       <c r="G271" s="3"/>
       <c r="H271" s="3"/>
     </row>
-    <row r="272" spans="1:8">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
